--- a/ig/DM-JUIN-2026/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>64</t>
+    <t>63</t>
   </si>
   <si>
     <t>Code</t>
@@ -572,9 +572,6 @@
   </si>
   <si>
     <t>Maîtrise du Facile à Lire et à Comprendre (FALC)</t>
-  </si>
-  <si>
-    <t>63</t>
   </si>
   <si>
     <t>Maitrise des outils informatisés à commande oculaire</t>
@@ -993,7 +990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1759,24 +1756,12 @@
         <v>61</v>
       </c>
       <c r="B64" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="C64" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="D64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="D65" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
